--- a/cet4/result/57_修仙校园_觉醒女帝的系统/57_修仙校园_觉醒女帝的系统_学习版.xlsx
+++ b/cet4/result/57_修仙校园_觉醒女帝的系统/57_修仙校园_觉醒女帝的系统_学习版.xlsx
@@ -397,759 +397,521 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D36"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>knob</v>
       </c>
       <c r="B2" t="str">
-        <v>knob</v>
+        <v>/nɑːb/</v>
       </c>
       <c r="C2" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D2" t="str">
         <v>把手</v>
       </c>
-      <c r="D2" t="str">
-        <v>knob(把手)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>butterfly</v>
       </c>
       <c r="B3" t="str">
-        <v>butterfly</v>
+        <v>/ˈbʌtərflaɪ/</v>
       </c>
       <c r="C3" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>蝴蝶</v>
       </c>
-      <c r="D3" t="str">
-        <v>butterfly(蝴蝶)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>deer</v>
       </c>
       <c r="B4" t="str">
-        <v>deer</v>
+        <v>/dɪr/</v>
       </c>
       <c r="C4" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>鹿</v>
       </c>
-      <c r="D4" t="str">
-        <v>deer(鹿)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>world</v>
       </c>
       <c r="B5" t="str">
-        <v>world</v>
+        <v>/wɜːrld/</v>
       </c>
       <c r="C5" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D5" t="str">
         <v>世界</v>
       </c>
-      <c r="D5" t="str">
-        <v>world(世界)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>common</v>
       </c>
       <c r="B6" t="str">
-        <v>common</v>
+        <v>/ˈkɑːmən/</v>
       </c>
       <c r="C6" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D6" t="str">
         <v>普通的</v>
       </c>
-      <c r="D6" t="str">
-        <v>common(普通的)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>rarely</v>
       </c>
       <c r="B7" t="str">
-        <v>rarely</v>
+        <v>/ˈrerli/</v>
       </c>
       <c r="C7" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D7" t="str">
         <v>很少</v>
       </c>
-      <c r="D7" t="str">
-        <v>rarely(很少)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>capacity</v>
       </c>
       <c r="B8" t="str">
-        <v>capacity</v>
+        <v>/kəˈpæsəti/</v>
       </c>
       <c r="C8" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D8" t="str">
         <v>能力</v>
       </c>
-      <c r="D8" t="str">
-        <v>capacity(能力)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>location</v>
       </c>
       <c r="B9" t="str">
-        <v>location</v>
+        <v>/loʊˈkeɪʃn/</v>
       </c>
       <c r="C9" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D9" t="str">
         <v>地点</v>
       </c>
-      <c r="D9" t="str">
-        <v>location(地点)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>subway</v>
       </c>
       <c r="B10" t="str">
-        <v>subway</v>
+        <v>/ˈsʌbweɪ/</v>
       </c>
       <c r="C10" t="str">
+        <v>n./vi.</v>
+      </c>
+      <c r="D10" t="str">
         <v>通道</v>
       </c>
-      <c r="D10" t="str">
-        <v>subway(通道)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>nose</v>
       </c>
       <c r="B11" t="str">
-        <v>nose</v>
+        <v>/noʊz/</v>
       </c>
       <c r="C11" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D11" t="str">
         <v>鼻子</v>
       </c>
-      <c r="D11" t="str">
-        <v>nose(鼻子)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>pipe</v>
       </c>
       <c r="B12" t="str">
-        <v>pipe</v>
+        <v>/paɪp/</v>
       </c>
       <c r="C12" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D12" t="str">
         <v>管</v>
       </c>
-      <c r="D12" t="str">
-        <v>pipe(管)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>threat</v>
       </c>
       <c r="B13" t="str">
-        <v>threat</v>
+        <v>/θret/</v>
       </c>
       <c r="C13" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D13" t="str">
         <v>威胁</v>
       </c>
-      <c r="D13" t="str">
-        <v>threat(威胁)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>deceive</v>
       </c>
       <c r="B14" t="str">
-        <v>deceive</v>
+        <v>/dɪˈsiːv/</v>
       </c>
       <c r="C14" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D14" t="str">
         <v>欺骗</v>
       </c>
-      <c r="D14" t="str">
-        <v>deceive(欺骗)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>whichever</v>
       </c>
       <c r="B15" t="str">
-        <v>whichever</v>
+        <v>/wɪtʃˈevər/</v>
       </c>
       <c r="C15" t="str">
+        <v>n./adj./pron.</v>
+      </c>
+      <c r="D15" t="str">
         <v>无论哪个</v>
       </c>
-      <c r="D15" t="str">
-        <v>whichever(无论哪个)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>file</v>
       </c>
       <c r="B16" t="str">
-        <v>file</v>
+        <v>/faɪl/</v>
       </c>
       <c r="C16" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D16" t="str">
         <v>文件</v>
       </c>
-      <c r="D16" t="str">
-        <v>file(文件)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>science</v>
       </c>
       <c r="B17" t="str">
-        <v>science</v>
+        <v>/ˈsaɪəns/</v>
       </c>
       <c r="C17" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D17" t="str">
         <v>科学</v>
       </c>
-      <c r="D17" t="str">
-        <v>science(科学)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>spade</v>
       </c>
       <c r="B18" t="str">
-        <v>spade</v>
+        <v>/speɪd/</v>
       </c>
       <c r="C18" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D18" t="str">
         <v>铲子</v>
       </c>
-      <c r="D18" t="str">
-        <v>spade(铲子)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>pipeline</v>
       </c>
       <c r="B19" t="str">
-        <v>location</v>
+        <v>/ˈpaɪplaɪn/</v>
       </c>
       <c r="C19" t="str">
-        <v>地点</v>
+        <v>n.</v>
       </c>
       <c r="D19" t="str">
-        <v>location(地点)📢</v>
+        <v>管道</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>cement</v>
       </c>
       <c r="B20" t="str">
-        <v>pipeline</v>
+        <v>/sɪˈment/</v>
       </c>
       <c r="C20" t="str">
-        <v>管道</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D20" t="str">
-        <v>pipeline(管道)📢</v>
+        <v>水泥</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>jar</v>
       </c>
       <c r="B21" t="str">
-        <v>cement</v>
+        <v>/dʒɑːr/</v>
       </c>
       <c r="C21" t="str">
-        <v>水泥</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D21" t="str">
-        <v>cement(水泥)📢</v>
+        <v>罐</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>crude</v>
       </c>
       <c r="B22" t="str">
-        <v>jar</v>
+        <v>/kruːd/</v>
       </c>
       <c r="C22" t="str">
-        <v>罐</v>
+        <v>n./adj.</v>
       </c>
       <c r="D22" t="str">
-        <v>jar(罐)📢</v>
+        <v>粗糙的</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>oar</v>
       </c>
       <c r="B23" t="str">
-        <v>crude</v>
+        <v>/ɔːr/</v>
       </c>
       <c r="C23" t="str">
-        <v>粗糙的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D23" t="str">
-        <v>crude(粗糙的)📢</v>
+        <v>桨</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>elbow</v>
       </c>
       <c r="B24" t="str">
-        <v>oar</v>
+        <v>/ˈelboʊ/</v>
       </c>
       <c r="C24" t="str">
-        <v>桨</v>
+        <v>n./vt.</v>
       </c>
       <c r="D24" t="str">
-        <v>oar(桨)📢</v>
+        <v>肘部</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>teaching</v>
       </c>
       <c r="B25" t="str">
-        <v>elbow</v>
+        <v>/ˈtiːtʃɪŋ/</v>
       </c>
       <c r="C25" t="str">
-        <v>肘部</v>
+        <v>n./v.</v>
       </c>
       <c r="D25" t="str">
-        <v>elbow(肘部)📢</v>
+        <v>教学</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>life</v>
       </c>
       <c r="B26" t="str">
-        <v>teaching</v>
+        <v>/laɪf/</v>
       </c>
       <c r="C26" t="str">
-        <v>教学</v>
+        <v>n.</v>
       </c>
       <c r="D26" t="str">
-        <v>teaching(教学)📢</v>
+        <v>生活</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>circular</v>
       </c>
       <c r="B27" t="str">
-        <v>butterfly</v>
+        <v>/ˈsɜːrkjələr/</v>
       </c>
       <c r="C27" t="str">
-        <v>蝴蝶</v>
+        <v>n./adj.</v>
       </c>
       <c r="D27" t="str">
-        <v>butterfly(蝴蝶)📢</v>
+        <v>圆形的</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>devote</v>
       </c>
       <c r="B28" t="str">
-        <v>life</v>
+        <v>/dɪˈvoʊt/</v>
       </c>
       <c r="C28" t="str">
-        <v>生活</v>
+        <v>v.</v>
       </c>
       <c r="D28" t="str">
-        <v>life(生活)📢</v>
+        <v>致力于</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>especially</v>
       </c>
       <c r="B29" t="str">
-        <v>circular</v>
+        <v>/ɪˈspeʃəli/</v>
       </c>
       <c r="C29" t="str">
-        <v>圆形的</v>
+        <v>v./adv.</v>
       </c>
       <c r="D29" t="str">
-        <v>circular(圆形的)📢</v>
+        <v>尤其</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>rid</v>
       </c>
       <c r="B30" t="str">
-        <v>devote</v>
+        <v>/rɪd/</v>
       </c>
       <c r="C30" t="str">
-        <v>致力于</v>
+        <v>n./v.</v>
       </c>
       <c r="D30" t="str">
-        <v>devote(致力于)📢</v>
+        <v>摆脱</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>weed</v>
       </c>
       <c r="B31" t="str">
-        <v>teaching</v>
+        <v>/wiːd/</v>
       </c>
       <c r="C31" t="str">
-        <v>教学</v>
+        <v>n./v.</v>
       </c>
       <c r="D31" t="str">
-        <v>teaching(教学)📢</v>
+        <v>杂草</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>fail</v>
       </c>
       <c r="B32" t="str">
-        <v>especially</v>
+        <v>/feɪl/</v>
       </c>
       <c r="C32" t="str">
-        <v>尤其</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D32" t="str">
-        <v>especially(尤其)📢</v>
+        <v>失败</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>whenever</v>
       </c>
       <c r="B33" t="str">
-        <v>butterfly</v>
+        <v>/wenˈevər/</v>
       </c>
       <c r="C33" t="str">
-        <v>蝴蝶</v>
+        <v>v./adv./conj.</v>
       </c>
       <c r="D33" t="str">
-        <v>butterfly(蝴蝶)📢</v>
+        <v>无论何时</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>write</v>
       </c>
       <c r="B34" t="str">
-        <v>rid</v>
+        <v>/raɪt/</v>
       </c>
       <c r="C34" t="str">
-        <v>摆脱</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D34" t="str">
-        <v>rid(摆脱)📢</v>
+        <v>写</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>swallow</v>
       </c>
       <c r="B35" t="str">
-        <v>weed</v>
+        <v>/ˈswɑːloʊ/</v>
       </c>
       <c r="C35" t="str">
-        <v>杂草</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D35" t="str">
-        <v>weed(杂草)📢</v>
+        <v>燕子</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>somebody</v>
       </c>
       <c r="B36" t="str">
-        <v>pipeline</v>
+        <v>/ˈsʌmbədi/</v>
       </c>
       <c r="C36" t="str">
-        <v>管道</v>
+        <v>n./pron.</v>
       </c>
       <c r="D36" t="str">
-        <v>pipeline(管道)📢</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37">
-        <v>36</v>
-      </c>
-      <c r="B37" t="str">
-        <v>fail</v>
-      </c>
-      <c r="C37" t="str">
-        <v>失败</v>
-      </c>
-      <c r="D37" t="str">
-        <v>fail(失败)📢</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38">
-        <v>37</v>
-      </c>
-      <c r="B38" t="str">
-        <v>threat</v>
-      </c>
-      <c r="C38" t="str">
-        <v>威胁</v>
-      </c>
-      <c r="D38" t="str">
-        <v>threat(威胁)📢</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39">
-        <v>38</v>
-      </c>
-      <c r="B39" t="str">
-        <v>jar</v>
-      </c>
-      <c r="C39" t="str">
-        <v>罐</v>
-      </c>
-      <c r="D39" t="str">
-        <v>jar(罐)📢</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40">
-        <v>39</v>
-      </c>
-      <c r="B40" t="str">
-        <v>capacity</v>
-      </c>
-      <c r="C40" t="str">
-        <v>能力</v>
-      </c>
-      <c r="D40" t="str">
-        <v>capacity(能力)📢</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41">
-        <v>40</v>
-      </c>
-      <c r="B41" t="str">
-        <v>whenever</v>
-      </c>
-      <c r="C41" t="str">
-        <v>无论何时</v>
-      </c>
-      <c r="D41" t="str">
-        <v>whenever(无论何时)📢</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42">
-        <v>41</v>
-      </c>
-      <c r="B42" t="str">
-        <v>write</v>
-      </c>
-      <c r="C42" t="str">
-        <v>写</v>
-      </c>
-      <c r="D42" t="str">
-        <v>write(写)📢</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43">
-        <v>42</v>
-      </c>
-      <c r="B43" t="str">
-        <v>butterfly</v>
-      </c>
-      <c r="C43" t="str">
-        <v>蝴蝶</v>
-      </c>
-      <c r="D43" t="str">
-        <v>butterfly(蝴蝶)📢</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44">
-        <v>43</v>
-      </c>
-      <c r="B44" t="str">
-        <v>swallow</v>
-      </c>
-      <c r="C44" t="str">
-        <v>燕子</v>
-      </c>
-      <c r="D44" t="str">
-        <v>swallow(燕子)📢</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45">
-        <v>44</v>
-      </c>
-      <c r="B45" t="str">
-        <v>rarely</v>
-      </c>
-      <c r="C45" t="str">
-        <v>很少</v>
-      </c>
-      <c r="D45" t="str">
-        <v>rarely(很少)📢</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46">
-        <v>45</v>
-      </c>
-      <c r="B46" t="str">
-        <v>circular</v>
-      </c>
-      <c r="C46" t="str">
-        <v>圆形的</v>
-      </c>
-      <c r="D46" t="str">
-        <v>circular(圆形的)📢</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47">
-        <v>46</v>
-      </c>
-      <c r="B47" t="str">
-        <v>somebody</v>
-      </c>
-      <c r="C47" t="str">
         <v>某人</v>
-      </c>
-      <c r="D47" t="str">
-        <v>somebody(某人)📢</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48" t="str">
-        <v>weed</v>
-      </c>
-      <c r="C48" t="str">
-        <v>杂草</v>
-      </c>
-      <c r="D48" t="str">
-        <v>weed(杂草)📢</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49" t="str">
-        <v>cement</v>
-      </c>
-      <c r="C49" t="str">
-        <v>水泥</v>
-      </c>
-      <c r="D49" t="str">
-        <v>cement(水泥)📢</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" t="str">
-        <v>teaching</v>
-      </c>
-      <c r="C50" t="str">
-        <v>教学</v>
-      </c>
-      <c r="D50" t="str">
-        <v>teaching(教学)📢</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" t="str">
-        <v>life</v>
-      </c>
-      <c r="C51" t="str">
-        <v>生活</v>
-      </c>
-      <c r="D51" t="str">
-        <v>life(生活)📢</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="str">
-        <v>jar</v>
-      </c>
-      <c r="C52" t="str">
-        <v>罐</v>
-      </c>
-      <c r="D52" t="str">
-        <v>jar(罐)📢</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="str">
-        <v>butterfly</v>
-      </c>
-      <c r="C53" t="str">
-        <v>蝴蝶</v>
-      </c>
-      <c r="D53" t="str">
-        <v>butterfly(蝴蝶)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D53"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D36"/>
   </ignoredErrors>
 </worksheet>
 </file>